--- a/tool/kintone-resourse-generator/run-list/新入社員研修.xlsx
+++ b/tool/kintone-resourse-generator/run-list/新入社員研修.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ishid\Desktop\project_management\tool\kintone-resourse-generator\run-list\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\run-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79ECE098-94AA-45E1-A2C3-8F446BB4ECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1074FFFC-2BD4-43DB-AC6E-6F249ED669D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>スペース識別名</t>
   </si>
@@ -45,21 +45,6 @@
         <charset val="128"/>
       </rPr>
       <t>クラススペース</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>L20_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>クラスｄｄスペース</t>
     </r>
     <phoneticPr fontId="2"/>
   </si>
@@ -440,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.109375" customWidth="1"/>
@@ -464,20 +449,9 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/tool/kintone-resourse-generator/run-list/新入社員研修.xlsx
+++ b/tool/kintone-resourse-generator/run-list/新入社員研修.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\run-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1074FFFC-2BD4-43DB-AC6E-6F249ED669D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4268547-4163-4CA8-A973-70818BB78614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>スペース識別名</t>
   </si>
@@ -28,38 +28,27 @@
     <t>スペーステンプレートID</t>
   </si>
   <si>
-    <t>設定テンプレート名</t>
-  </si>
-  <si>
     <t>class-space</t>
   </si>
   <si>
-    <r>
-      <t>L20_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>クラススペース</t>
-    </r>
-    <phoneticPr fontId="2"/>
+    <t>設定テンプレート名（基本）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定テンプレート名（カスタム）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>L20_クラススペース</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -76,9 +65,11 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -109,8 +100,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -425,15 +416,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.109375" customWidth="1"/>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,22 +434,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tool/kintone-resourse-generator/run-list/新入社員研修.xlsx
+++ b/tool/kintone-resourse-generator/run-list/新入社員研修.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\run-list\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4268547-4163-4CA8-A973-70818BB78614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D912E1-60D9-481D-9781-71226CC46CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>スペース識別名</t>
   </si>
   <si>
     <t>スペーステンプレートID</t>
-  </si>
-  <si>
-    <t>class-space</t>
   </si>
   <si>
     <t>設定テンプレート名（基本）</t>
@@ -39,7 +36,15 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>L20_クラススペース</t>
+    <t>クラススペース</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラススペース_L01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>L01</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -434,21 +439,24 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
